--- a/artfynd/A 22377-2025 artfynd.xlsx
+++ b/artfynd/A 22377-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17281159</v>
+        <v>117614614</v>
       </c>
       <c r="B2" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1205</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storsvedjemyran, Mpd</t>
+          <t>Blomsteråsen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>606633.7185734808</v>
+        <v>606571</v>
       </c>
       <c r="R2" t="n">
-        <v>6958370.235320631</v>
+        <v>6958473</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-08-31</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-08-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,62 +756,48 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Lövrik skog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Caroline Westerlund</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>17280076</v>
+        <v>17281159</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -844,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>606633.7185734808</v>
+        <v>606634</v>
       </c>
       <c r="R3" t="n">
-        <v>6958370.235320631</v>
+        <v>6958370</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -877,19 +844,9 @@
           <t>2012-08-31</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-08-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,15 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>17280069</v>
+        <v>117614616</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,41 +893,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Storsvedjemyran, Mpd</t>
+          <t>Blomsteråsen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>606633.7185734808</v>
+        <v>606776</v>
       </c>
       <c r="R4" t="n">
-        <v>6958370.235320631</v>
+        <v>6958117</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,22 +947,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2012-08-31</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2012-08-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,40 +963,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Lövrik skog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Caroline Westerlund</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>17281158</v>
       </c>
       <c r="B5" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,10 +1018,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>606633.7185734808</v>
+        <v>606634</v>
       </c>
       <c r="R5" t="n">
-        <v>6958370.235320631</v>
+        <v>6958370</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1127,19 +1051,9 @@
           <t>2012-08-31</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2012-08-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,53 +1089,52 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117614615</v>
+        <v>17280076</v>
       </c>
       <c r="B6" t="n">
-        <v>90519</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Blomsteråsen, Mpd</t>
+          <t>Storsvedjemyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>606748</v>
+        <v>606634</v>
       </c>
       <c r="R6" t="n">
-        <v>6958166</v>
+        <v>6958370</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1245,12 +1158,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2012-08-31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2012-08-31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,31 +1174,35 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Lövrik skog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Caroline Westerlund</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Via Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117614614</v>
+        <v>17280069</v>
       </c>
       <c r="B7" t="n">
-        <v>90784</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1293,37 +1210,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Blomsteråsen, Mpd</t>
+          <t>Storsvedjemyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>606571</v>
+        <v>606634</v>
       </c>
       <c r="R7" t="n">
-        <v>6958473</v>
+        <v>6958370</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1347,12 +1268,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2012-08-31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2012-08-31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,121 +1284,28 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Lövrik skog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Caroline Westerlund</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>117614616</v>
-      </c>
-      <c r="B8" t="n">
-        <v>82261</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Blomsteråsen, Mpd</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>606776</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6958117</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Timrå</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Medelpad</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Ljustorp</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2024-06-04</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2024-06-04</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Maria Edstam</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Maria Edstam</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Via Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22377-2025 artfynd.xlsx
+++ b/artfynd/A 22377-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117614614</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17281159</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117614616</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1086,6 +1106,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17281158</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1196,6 +1221,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17280076</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1306,8 +1336,21 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17280069</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>